--- a/data/trans_orig/P19C09-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P19C09-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por otros motivos en 2007</t>
+          <t>Población según si el motivo por su última visita al dentista fue por otros motivos en 2007 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16920</t>
+          <t>16893</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35585</t>
+          <t>35890</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35348</t>
+          <t>35745</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>61492</t>
+          <t>61379</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57877</t>
+          <t>57026</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>89072</t>
+          <t>90434</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>652740</t>
+          <t>652435</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>671405</t>
+          <t>671432</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>897467</t>
+          <t>897580</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>923611</t>
+          <t>923214</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1558212</t>
+          <t>1556850</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1589407</t>
+          <t>1590258</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21307</t>
+          <t>21824</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45605</t>
+          <t>46072</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15487</t>
+          <t>15815</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36281</t>
+          <t>36455</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42822</t>
+          <t>41715</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>75522</t>
+          <t>72755</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1265632</t>
+          <t>1265165</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1289930</t>
+          <t>1289413</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1334250</t>
+          <t>1334076</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1355044</t>
+          <t>1354716</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2606246</t>
+          <t>2609013</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2638946</t>
+          <t>2640053</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,44%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2876</t>
+          <t>3451</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14032</t>
+          <t>15742</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7775</t>
+          <t>8218</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23497</t>
+          <t>25672</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13840</t>
+          <t>14427</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33685</t>
+          <t>34158</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>436897</t>
+          <t>435187</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>448053</t>
+          <t>447478</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>384268</t>
+          <t>382093</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>399990</t>
+          <t>399547</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>825009</t>
+          <t>824536</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>844854</t>
+          <t>844267</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49747</t>
+          <t>49811</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80395</t>
+          <t>80461</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69534</t>
+          <t>68707</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>106829</t>
+          <t>105070</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>126092</t>
+          <t>127168</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>178096</t>
+          <t>175380</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2370096</t>
+          <t>2370030</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2400744</t>
+          <t>2400680</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2630426</t>
+          <t>2632185</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2667721</t>
+          <t>2668548</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5009649</t>
+          <t>5012365</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5061653</t>
+          <t>5060577</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,55%</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por otros motivos en 2012</t>
+          <t>Población según si el motivo por su última visita al dentista fue por otros motivos en 2012 (tasa de respuesta: 97,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8013</t>
+          <t>7304</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25605</t>
+          <t>23879</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22406</t>
+          <t>22485</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45368</t>
+          <t>46830</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34424</t>
+          <t>34492</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64129</t>
+          <t>63503</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>740085</t>
+          <t>741811</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>757677</t>
+          <t>758386</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1065689</t>
+          <t>1064227</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1088651</t>
+          <t>1088572</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1812618</t>
+          <t>1813244</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1842323</t>
+          <t>1842255</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12532</t>
+          <t>12940</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31787</t>
+          <t>32195</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28760</t>
+          <t>28566</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54412</t>
+          <t>55746</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45837</t>
+          <t>45142</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>78794</t>
+          <t>78586</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1608489</t>
+          <t>1608081</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1627744</t>
+          <t>1627336</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1488314</t>
+          <t>1486980</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1513966</t>
+          <t>1514160</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3104208</t>
+          <t>3104416</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3137165</t>
+          <t>3137860</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7035</t>
+          <t>7794</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23902</t>
+          <t>23554</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7356</t>
+          <t>7727</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23539</t>
+          <t>22843</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17602</t>
+          <t>17970</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39415</t>
+          <t>39990</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>401778</t>
+          <t>402126</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>418645</t>
+          <t>417886</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>388783</t>
+          <t>389479</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>404966</t>
+          <t>404595</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>798587</t>
+          <t>798012</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>820400</t>
+          <t>820032</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36061</t>
+          <t>34796</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65157</t>
+          <t>63611</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67139</t>
+          <t>68651</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>107951</t>
+          <t>108373</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>112286</t>
+          <t>112826</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>160284</t>
+          <t>161484</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2766489</t>
+          <t>2768035</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2795585</t>
+          <t>2796850</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2958154</t>
+          <t>2957732</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2998966</t>
+          <t>2997454</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5737468</t>
+          <t>5736268</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5785466</t>
+          <t>5784926</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por otros motivos en 2016</t>
+          <t>Población según si el motivo por su última visita al dentista fue por otros motivos en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7729</t>
+          <t>8169</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22544</t>
+          <t>21846</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13572</t>
+          <t>14659</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32835</t>
+          <t>32785</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25564</t>
+          <t>26289</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49605</t>
+          <t>48359</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>434875</t>
+          <t>435573</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>449690</t>
+          <t>449250</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>606039</t>
+          <t>606089</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>625302</t>
+          <t>624215</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1046688</t>
+          <t>1047934</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1070729</t>
+          <t>1070004</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,6%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36013</t>
+          <t>36624</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64859</t>
+          <t>66328</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22786</t>
+          <t>22180</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45290</t>
+          <t>45854</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64605</t>
+          <t>64463</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>101012</t>
+          <t>104224</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1631746</t>
+          <t>1630277</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1660592</t>
+          <t>1659981</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1663429</t>
+          <t>1662865</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1685933</t>
+          <t>1686539</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3304312</t>
+          <t>3301100</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3340719</t>
+          <t>3340861</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7374</t>
+          <t>7398</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22561</t>
+          <t>23161</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13566</t>
+          <t>13702</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34113</t>
+          <t>33423</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24203</t>
+          <t>24105</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48221</t>
+          <t>48492</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -4737,12 +4737,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>476683</t>
+          <t>476083</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>491870</t>
+          <t>491846</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>474207</t>
+          <t>474897</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>494754</t>
+          <t>494618</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>959343</t>
+          <t>959072</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>983361</t>
+          <t>983459</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61486</t>
+          <t>61100</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95891</t>
+          <t>94582</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59980</t>
+          <t>59923</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>95819</t>
+          <t>95973</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>127493</t>
+          <t>128331</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>177927</t>
+          <t>176754</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2557378</t>
+          <t>2558687</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2591783</t>
+          <t>2592169</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2760094</t>
+          <t>2759940</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2795933</t>
+          <t>2795990</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5331255</t>
+          <t>5332428</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5381689</t>
+          <t>5380851</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C09-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P19C09-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16893</t>
+          <t>16132</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35890</t>
+          <t>35739</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35745</t>
+          <t>35067</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>61379</t>
+          <t>61648</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57026</t>
+          <t>58100</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>90434</t>
+          <t>90120</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>652435</t>
+          <t>652586</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>671432</t>
+          <t>672193</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>897580</t>
+          <t>897311</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>923214</t>
+          <t>923892</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1556850</t>
+          <t>1557164</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1590258</t>
+          <t>1589184</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,47%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21824</t>
+          <t>21504</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46072</t>
+          <t>47030</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15815</t>
+          <t>15398</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36455</t>
+          <t>35464</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41715</t>
+          <t>42564</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72755</t>
+          <t>73744</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1265165</t>
+          <t>1264207</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1289413</t>
+          <t>1289733</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1334076</t>
+          <t>1335067</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1354716</t>
+          <t>1355133</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2609013</t>
+          <t>2608024</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2640053</t>
+          <t>2639204</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3451</t>
+          <t>2702</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15742</t>
+          <t>14480</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8218</t>
+          <t>7885</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25672</t>
+          <t>24591</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14427</t>
+          <t>13695</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34158</t>
+          <t>33207</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>435187</t>
+          <t>436449</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>447478</t>
+          <t>448227</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>382093</t>
+          <t>383174</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>399547</t>
+          <t>399880</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>824536</t>
+          <t>825487</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>844267</t>
+          <t>844999</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49811</t>
+          <t>49727</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80461</t>
+          <t>81908</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68707</t>
+          <t>69568</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>105070</t>
+          <t>105202</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>127168</t>
+          <t>126470</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>175380</t>
+          <t>175335</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2370030</t>
+          <t>2368583</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2400680</t>
+          <t>2400764</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2632185</t>
+          <t>2632053</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2668548</t>
+          <t>2667687</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5012365</t>
+          <t>5012410</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5060577</t>
+          <t>5061275</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,56%</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7304</t>
+          <t>7789</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23879</t>
+          <t>25282</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22485</t>
+          <t>22674</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46830</t>
+          <t>45652</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34492</t>
+          <t>34894</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63503</t>
+          <t>63973</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>741811</t>
+          <t>740408</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>758386</t>
+          <t>757901</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1064227</t>
+          <t>1065405</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1088572</t>
+          <t>1088383</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1813244</t>
+          <t>1812774</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1842255</t>
+          <t>1841853</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12940</t>
+          <t>12837</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32195</t>
+          <t>32761</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28566</t>
+          <t>28428</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55746</t>
+          <t>55217</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45142</t>
+          <t>46431</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>78586</t>
+          <t>79569</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1608081</t>
+          <t>1607515</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1627336</t>
+          <t>1627439</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1486980</t>
+          <t>1487509</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1514160</t>
+          <t>1514298</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3104416</t>
+          <t>3103433</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3137860</t>
+          <t>3136571</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7794</t>
+          <t>7261</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23554</t>
+          <t>23478</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,47 +3036,47 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,52%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>13215</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7547</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>23434</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3,21%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>1,83%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,53%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>13215</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>7727</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>22843</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,21%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17970</t>
+          <t>17932</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39990</t>
+          <t>39680</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>402126</t>
+          <t>402202</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>417886</t>
+          <t>418419</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,49 +3149,49 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>98,29%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>399107</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>388888</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>404775</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>96,79%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>94,32%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>98,17%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>399107</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>389479</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>404595</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,79%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>94,46%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>98,13%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>735</t>
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>798012</t>
+          <t>798322</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>820032</t>
+          <t>820070</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34796</t>
+          <t>35566</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63611</t>
+          <t>66818</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68651</t>
+          <t>68636</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>108373</t>
+          <t>106160</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>112826</t>
+          <t>112086</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>161484</t>
+          <t>159629</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2768035</t>
+          <t>2764828</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2796850</t>
+          <t>2796080</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2957732</t>
+          <t>2959945</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2997454</t>
+          <t>2997469</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5736268</t>
+          <t>5738123</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5784926</t>
+          <t>5785666</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8169</t>
+          <t>7926</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21846</t>
+          <t>21477</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14659</t>
+          <t>14339</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32785</t>
+          <t>34243</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26289</t>
+          <t>25880</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48359</t>
+          <t>50181</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>435573</t>
+          <t>435942</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>449250</t>
+          <t>449493</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>606089</t>
+          <t>604631</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>624215</t>
+          <t>624535</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1047934</t>
+          <t>1046112</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1070004</t>
+          <t>1070413</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,64%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36624</t>
+          <t>36410</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66328</t>
+          <t>64836</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22180</t>
+          <t>21487</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45854</t>
+          <t>46724</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64463</t>
+          <t>64326</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>104224</t>
+          <t>99655</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1630277</t>
+          <t>1631769</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1659981</t>
+          <t>1660195</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1662865</t>
+          <t>1661995</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1686539</t>
+          <t>1687232</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3301100</t>
+          <t>3305669</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3340861</t>
+          <t>3340998</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4624,12 +4624,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7398</t>
+          <t>6706</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23161</t>
+          <t>22621</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13702</t>
+          <t>13639</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33423</t>
+          <t>32241</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24105</t>
+          <t>25069</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48492</t>
+          <t>48453</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4737,12 +4737,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>476083</t>
+          <t>476623</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>491846</t>
+          <t>492538</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>474897</t>
+          <t>476079</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>494618</t>
+          <t>494681</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>959072</t>
+          <t>959111</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>983459</t>
+          <t>982495</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,51%</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61100</t>
+          <t>60991</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>94582</t>
+          <t>95449</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59923</t>
+          <t>60045</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>95973</t>
+          <t>96129</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>128331</t>
+          <t>128549</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>176754</t>
+          <t>180379</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2558687</t>
+          <t>2557820</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2592169</t>
+          <t>2592278</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2759940</t>
+          <t>2759784</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2795990</t>
+          <t>2795868</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5332428</t>
+          <t>5328803</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5380851</t>
+          <t>5380633</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
